--- a/src/test/resources/api_data/datasets/dataset_patch.xlsx
+++ b/src/test/resources/api_data/datasets/dataset_patch.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gmena\Java_DEMO\Herokuapp\src\test\resources\api_data\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE2DF6C-DC04-4792-890C-130F173413D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF04D546-2031-446B-AFFF-772B2106AB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>firstName</t>
   </si>
@@ -109,211 +109,12 @@
   </si>
   <si>
     <t>12345678901</t>
-  </si>
-  <si>
-    <t>69ccea4a23b8a000159cb16c</t>
-  </si>
-  <si>
-    <t>69ccea4c23b8a000159cb16d</t>
-  </si>
-  <si>
-    <t>69ccea4ee174bc00158a27a1</t>
-  </si>
-  <si>
-    <t>69ccea50e174bc00158a27a3</t>
-  </si>
-  <si>
-    <t>69ccea5223b8a000159cb16f</t>
-  </si>
-  <si>
-    <t>69cceb6423b8a000159cb170</t>
-  </si>
-  <si>
-    <t>69cceb66e174bc00158a27a7</t>
-  </si>
-  <si>
-    <t>69cceb6823b8a000159cb171</t>
-  </si>
-  <si>
-    <t>69cceb6ae174bc00158a27a9</t>
-  </si>
-  <si>
-    <t>69cceb6c23b8a000159cb174</t>
-  </si>
-  <si>
-    <t>69ccf3e923b8a000159cb18c</t>
-  </si>
-  <si>
-    <t>69ccf41f23b8a000159cb1a9</t>
-  </si>
-  <si>
-    <t>69ccf421e174bc00158a27f1</t>
-  </si>
-  <si>
-    <t>69ccf423e174bc00158a27f2</t>
-  </si>
-  <si>
-    <t>69ccf425e174bc00158a27f3</t>
-  </si>
-  <si>
-    <t>69ccf427e174bc00158a27f5</t>
-  </si>
-  <si>
-    <t>69ccf42923b8a000159cb1ad</t>
-  </si>
-  <si>
-    <t>69ccf42be174bc00158a27f8</t>
-  </si>
-  <si>
-    <t>69ccf42d23b8a000159cb1af</t>
-  </si>
-  <si>
-    <t>69ccf42f23b8a000159cb1b0</t>
-  </si>
-  <si>
-    <t>69ccf431e174bc00158a27fb</t>
-  </si>
-  <si>
-    <t>69ccf433e174bc00158a27fd</t>
-  </si>
-  <si>
-    <t>69ccf435e174bc00158a2801</t>
-  </si>
-  <si>
-    <t>69ccf43823b8a000159cb1b5</t>
-  </si>
-  <si>
-    <t>69ccf43a23b8a000159cb1b7</t>
-  </si>
-  <si>
-    <t>69ccf43ce174bc00158a2802</t>
-  </si>
-  <si>
-    <t>69ccf43e23b8a000159cb1bb</t>
-  </si>
-  <si>
-    <t>69ccf44723b8a000159cb1bf</t>
-  </si>
-  <si>
-    <t>69ccfd43e174bc00158a284e</t>
-  </si>
-  <si>
-    <t>69ccfd79e174bc00158a2853</t>
-  </si>
-  <si>
-    <t>69ccfe69e174bc00158a285e</t>
-  </si>
-  <si>
-    <t>69ccfe9fe174bc00158a2887</t>
-  </si>
-  <si>
-    <t>69ccfea123b8a000159cb232</t>
-  </si>
-  <si>
-    <t>69ccfea3e174bc00158a288a</t>
-  </si>
-  <si>
-    <t>69ccfea5e174bc00158a288b</t>
-  </si>
-  <si>
-    <t>69ccfea723b8a000159cb234</t>
-  </si>
-  <si>
-    <t>69ccfea9e174bc00158a288d</t>
-  </si>
-  <si>
-    <t>69ccfeabe174bc00158a288f</t>
-  </si>
-  <si>
-    <t>69ccfead23b8a000159cb236</t>
-  </si>
-  <si>
-    <t>69ccfeafe174bc00158a2892</t>
-  </si>
-  <si>
-    <t>69ccfeb1e174bc00158a2893</t>
-  </si>
-  <si>
-    <t>69ccfeb423b8a000159cb238</t>
-  </si>
-  <si>
-    <t>69ccfeb6e174bc00158a2896</t>
-  </si>
-  <si>
-    <t>69ccfeb823b8a000159cb239</t>
-  </si>
-  <si>
-    <t>69ccfebae174bc00158a2899</t>
-  </si>
-  <si>
-    <t>69ccfebc23b8a000159cb23a</t>
-  </si>
-  <si>
-    <t>69ccfebe23b8a000159cb23b</t>
-  </si>
-  <si>
-    <t>69ccfec623b8a000159cb23e</t>
-  </si>
-  <si>
-    <t>69ccff6823b8a000159cb254</t>
-  </si>
-  <si>
-    <t>69ccff9e23b8a000159cb271</t>
-  </si>
-  <si>
-    <t>69ccffa0e174bc00158a28d9</t>
-  </si>
-  <si>
-    <t>69ccffa2e174bc00158a28da</t>
-  </si>
-  <si>
-    <t>69ccffa423b8a000159cb275</t>
-  </si>
-  <si>
-    <t>69ccffa6e174bc00158a28dc</t>
-  </si>
-  <si>
-    <t>69ccffa823b8a000159cb276</t>
-  </si>
-  <si>
-    <t>69ccffaae174bc00158a28de</t>
-  </si>
-  <si>
-    <t>69ccffac23b8a000159cb278</t>
-  </si>
-  <si>
-    <t>69ccffae23b8a000159cb279</t>
-  </si>
-  <si>
-    <t>69ccffb0e174bc00158a28e1</t>
-  </si>
-  <si>
-    <t>69ccffb2e174bc00158a28e2</t>
-  </si>
-  <si>
-    <t>69ccffb4e174bc00158a28e3</t>
-  </si>
-  <si>
-    <t>69ccffb623b8a000159cb27e</t>
-  </si>
-  <si>
-    <t>69ccffb8e174bc00158a28e5</t>
-  </si>
-  <si>
-    <t>69ccffbae174bc00158a28e6</t>
-  </si>
-  <si>
-    <t>69ccffbce174bc00158a28e8</t>
-  </si>
-  <si>
-    <t>69ccffc5e174bc00158a28eb</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -691,13 +492,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="1"/>
@@ -706,10 +504,7 @@
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1"/>
@@ -718,10 +513,7 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="1"/>
@@ -730,113 +522,71 @@
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s" s="0">
-        <v>84</v>
-      </c>
       <c r="D5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="E6" t="s" s="0">
+      <c r="E6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s" s="0">
-        <v>86</v>
-      </c>
       <c r="F7" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="G8" t="s" s="0">
+      <c r="G8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s" s="0">
-        <v>88</v>
-      </c>
-      <c r="H9" t="s" s="0">
+      <c r="H9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="I10" t="s" s="0">
+      <c r="I10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s" s="0">
-        <v>90</v>
-      </c>
       <c r="J11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="K12" t="s" s="0">
+      <c r="K12" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="L13" t="s" s="0">
+      <c r="L13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s" s="0">
-        <v>77</v>
-      </c>
       <c r="D15" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s" s="0">
-        <v>78</v>
-      </c>
-      <c r="E16" t="s" s="0">
+      <c r="E16" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s" s="0">
-        <v>79</v>
-      </c>
       <c r="F17" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s" s="0">
-        <v>80</v>
-      </c>
       <c r="J18" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s" s="0">
-        <v>81</v>
-      </c>
       <c r="J19" s="1" t="s">
         <v>26</v>
       </c>
